--- a/docs/product_backlog/product backlog template.xlsx
+++ b/docs/product_backlog/product backlog template.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DC266036-F164-447E-8A2D-849A02AD8F39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3154419B-EB0F-4ED3-8570-2D953C21A1B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="21806" windowHeight="13886" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="116">
   <si>
     <t>Story ID</t>
   </si>
@@ -291,9 +291,6 @@
     <t>As an MO, I want the AI to match skills between jobs and applicants, So that I can quickly identify top candidates.</t>
   </si>
   <si>
-    <t>As an MO, I want the AI to automatically identify and highlight the key skills an applicant is missing, So that I can quickly assess their skill gaps without manual cross-checking.</t>
-  </si>
-  <si>
     <t>1. MO can create a job posting.
 2. Job includes required skills.</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -336,9 +333,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Check TA Overall Workload</t>
-  </si>
-  <si>
     <t>As an Admin, I want to check TAs' overall workload across all modules, So that I can identify if any single TA has taken on excessive positions.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -417,6 +411,66 @@
   </si>
   <si>
     <t>Admin Survey</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>As an MO, I want the AI to automatically identify and highlight the key skills an applicant is missing, So that I can quickly assess their skill gaps without manual cross-checking.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Check TA Overall Workload</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.3.23</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.3.29</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.3.30</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.4.3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.4.10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.4.6</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.4.13</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.4.19</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.5.4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.5.10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.4.5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.4.16</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.4.1</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -828,21 +882,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q22"/>
-  <sheetFormatPr defaultColWidth="8.84375" defaultRowHeight="14.15" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.84375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.07421875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.23046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="27.3046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.3046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.9296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.86328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.06640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.19921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.9296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.9296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.73046875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.73046875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="28.3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" ht="27" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -874,7 +928,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="99" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17" ht="97.15" x14ac:dyDescent="0.4">
       <c r="A2" s="4"/>
       <c r="B2" s="4"/>
       <c r="C2" s="4" t="s">
@@ -897,7 +951,7 @@
       <c r="P2" s="5"/>
       <c r="Q2" s="5"/>
     </row>
-    <row r="3" spans="1:17" ht="70.75" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" ht="55.5" x14ac:dyDescent="0.4">
       <c r="A3" s="6" t="s">
         <v>17</v>
       </c>
@@ -922,10 +976,12 @@
       <c r="H3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="8">
-        <v>46091</v>
-      </c>
-      <c r="J3" s="4"/>
+      <c r="I3" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>104</v>
+      </c>
       <c r="K3" s="5"/>
       <c r="L3" s="5"/>
       <c r="M3" s="5"/>
@@ -934,7 +990,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
     </row>
-    <row r="4" spans="1:17" ht="56.6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" ht="55.5" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
         <v>18</v>
       </c>
@@ -959,8 +1015,12 @@
       <c r="H4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
+      <c r="I4" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>104</v>
+      </c>
       <c r="K4" s="5"/>
       <c r="L4" s="5"/>
       <c r="M4" s="5"/>
@@ -969,7 +1029,7 @@
       <c r="P4" s="5"/>
       <c r="Q4" s="5"/>
     </row>
-    <row r="5" spans="1:17" ht="70.75" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:17" ht="69.400000000000006" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
         <v>19</v>
       </c>
@@ -994,8 +1054,12 @@
       <c r="H5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
+      <c r="I5" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>104</v>
+      </c>
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
       <c r="M5" s="5"/>
@@ -1004,7 +1068,7 @@
       <c r="P5" s="5"/>
       <c r="Q5" s="5"/>
     </row>
-    <row r="6" spans="1:17" ht="70.75" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:17" ht="55.5" x14ac:dyDescent="0.4">
       <c r="A6" s="4" t="s">
         <v>20</v>
       </c>
@@ -1029,8 +1093,12 @@
       <c r="H6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
+      <c r="I6" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>106</v>
+      </c>
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
       <c r="M6" s="5"/>
@@ -1039,7 +1107,7 @@
       <c r="P6" s="5"/>
       <c r="Q6" s="5"/>
     </row>
-    <row r="7" spans="1:17" ht="84.9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:17" ht="69.400000000000006" x14ac:dyDescent="0.4">
       <c r="A7" s="4" t="s">
         <v>21</v>
       </c>
@@ -1064,8 +1132,12 @@
       <c r="H7" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
+      <c r="I7" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>107</v>
+      </c>
       <c r="K7" s="5"/>
       <c r="L7" s="5"/>
       <c r="M7" s="5"/>
@@ -1074,7 +1146,7 @@
       <c r="P7" s="5"/>
       <c r="Q7" s="5"/>
     </row>
-    <row r="8" spans="1:17" ht="70.75" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:17" ht="55.5" x14ac:dyDescent="0.4">
       <c r="A8" s="4" t="s">
         <v>22</v>
       </c>
@@ -1099,8 +1171,12 @@
       <c r="H8" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
+      <c r="I8" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>107</v>
+      </c>
       <c r="K8" s="5"/>
       <c r="L8" s="5"/>
       <c r="M8" s="5"/>
@@ -1109,7 +1185,7 @@
       <c r="P8" s="5"/>
       <c r="Q8" s="5"/>
     </row>
-    <row r="9" spans="1:17" ht="70.75" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:17" ht="55.5" x14ac:dyDescent="0.4">
       <c r="A9" s="4" t="s">
         <v>23</v>
       </c>
@@ -1134,8 +1210,12 @@
       <c r="H9" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
+      <c r="I9" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>110</v>
+      </c>
       <c r="K9" s="5"/>
       <c r="L9" s="5"/>
       <c r="M9" s="5"/>
@@ -1144,7 +1224,7 @@
       <c r="P9" s="5"/>
       <c r="Q9" s="5"/>
     </row>
-    <row r="10" spans="1:17" ht="56.6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:17" ht="55.5" x14ac:dyDescent="0.4">
       <c r="A10" s="4" t="s">
         <v>24</v>
       </c>
@@ -1169,8 +1249,12 @@
       <c r="H10" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
+      <c r="I10" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>107</v>
+      </c>
       <c r="K10" s="5"/>
       <c r="L10" s="5"/>
       <c r="M10" s="5"/>
@@ -1179,7 +1263,7 @@
       <c r="P10" s="5"/>
       <c r="Q10" s="5"/>
     </row>
-    <row r="11" spans="1:17" ht="56.6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:17" ht="55.5" x14ac:dyDescent="0.4">
       <c r="A11" s="4" t="s">
         <v>25</v>
       </c>
@@ -1204,8 +1288,12 @@
       <c r="H11" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
+      <c r="I11" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>112</v>
+      </c>
       <c r="K11" s="5"/>
       <c r="L11" s="5"/>
       <c r="M11" s="5"/>
@@ -1214,7 +1302,7 @@
       <c r="P11" s="5"/>
       <c r="Q11" s="5"/>
     </row>
-    <row r="12" spans="1:17" ht="56.6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:17" s="5" customFormat="1" ht="55.5" x14ac:dyDescent="0.4">
       <c r="A12" s="4" t="s">
         <v>56</v>
       </c>
@@ -1231,7 +1319,7 @@
         <v>1</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G12" s="4">
         <v>3</v>
@@ -1239,8 +1327,14 @@
       <c r="H12" s="4" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" ht="70.75" x14ac:dyDescent="0.35">
+      <c r="I12" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" s="5" customFormat="1" ht="55.5" x14ac:dyDescent="0.4">
       <c r="A13" s="4" t="s">
         <v>57</v>
       </c>
@@ -1257,16 +1351,22 @@
         <v>3</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G13" s="4">
         <v>5</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" ht="70.75" x14ac:dyDescent="0.35">
+        <v>79</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" s="5" customFormat="1" ht="55.5" x14ac:dyDescent="0.4">
       <c r="A14" s="4" t="s">
         <v>58</v>
       </c>
@@ -1283,7 +1383,7 @@
         <v>1</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G14" s="4">
         <v>3</v>
@@ -1291,8 +1391,14 @@
       <c r="H14" s="4" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" ht="56.6" x14ac:dyDescent="0.35">
+      <c r="I14" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" s="5" customFormat="1" ht="55.5" x14ac:dyDescent="0.4">
       <c r="A15" s="4" t="s">
         <v>59</v>
       </c>
@@ -1309,16 +1415,22 @@
         <v>3</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G15" s="4">
         <v>2</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" ht="70.75" x14ac:dyDescent="0.35">
+        <v>79</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" s="5" customFormat="1" ht="55.5" x14ac:dyDescent="0.4">
       <c r="A16" s="4" t="s">
         <v>60</v>
       </c>
@@ -1335,16 +1447,22 @@
         <v>2</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G16" s="4">
         <v>5</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="99" x14ac:dyDescent="0.35">
+        <v>80</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" s="5" customFormat="1" ht="97.15" x14ac:dyDescent="0.4">
       <c r="A17" s="4" t="s">
         <v>61</v>
       </c>
@@ -1352,7 +1470,7 @@
         <v>67</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>36</v>
@@ -1361,143 +1479,179 @@
         <v>2</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G17" s="4">
         <v>5</v>
       </c>
       <c r="H17" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" s="5" customFormat="1" ht="69.400000000000006" x14ac:dyDescent="0.4">
+      <c r="A18" s="4" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" ht="99" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
+      <c r="B18" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="C18" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="B18" t="s">
+      <c r="D18" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E18" s="4">
+        <v>1</v>
+      </c>
+      <c r="F18" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="G18" s="4">
+        <v>5</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="J18" s="8" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" s="5" customFormat="1" ht="69.400000000000006" x14ac:dyDescent="0.4">
+      <c r="A19" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E18" s="1">
-        <v>1</v>
-      </c>
-      <c r="F18" s="1" t="s">
+      <c r="B19" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E19" s="4">
+        <v>2</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="G19" s="4">
+        <v>3</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" s="5" customFormat="1" ht="83.25" x14ac:dyDescent="0.4">
+      <c r="A20" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="G18" s="1">
+      <c r="B20" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E20" s="4">
+        <v>4</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="G20" s="4">
+        <v>3</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="J20" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" s="5" customFormat="1" ht="69.400000000000006" x14ac:dyDescent="0.4">
+      <c r="A21" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E21" s="4">
+        <v>2</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="G21" s="4">
+        <v>2</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="J21" s="8" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" s="5" customFormat="1" ht="97.15" x14ac:dyDescent="0.4">
+      <c r="A22" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E22" s="4">
+        <v>3</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G22" s="4">
         <v>5</v>
       </c>
-      <c r="H18" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="84.9" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E19" s="1">
-        <v>2</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="G19" s="1">
-        <v>3</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="99" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E20" s="1">
-        <v>4</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="G20" s="1">
-        <v>3</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="84.9" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E21" s="1">
-        <v>2</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="G21" s="1">
-        <v>2</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="113.15" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E22" s="1">
-        <v>3</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="G22" s="1">
-        <v>5</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>81</v>
+      <c r="H22" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="J22" s="8" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>
